--- a/InputData/bldgs/MDSC/Max Distrib Solar Capacity.xlsx
+++ b/InputData/bldgs/MDSC/Max Distrib Solar Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\bldgs\MDSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\MDSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EDDF81-4ECF-40FF-859E-C2B6ED57C28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F63061-1373-47A1-9DAE-7ACF18DFB3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29640" yWindow="1095" windowWidth="25275" windowHeight="13380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="278">
   <si>
     <t>MDSC Maximum Distributed Solar Capacity</t>
   </si>
@@ -1045,6 +1045,15 @@
   </si>
   <si>
     <t>This variable helps control the rooftop-solar buildout lever. It represents the maximum technical potential</t>
+  </si>
+  <si>
+    <t>data centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. The model does not build distributed solar at data centers, so their maximum distributed capacity is zero for every source.</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1332,7 @@
       <alignment wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1417,6 +1426,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="8">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Body: normal cell" xfId="6" xr:uid="{CDCA09DE-4916-4FC2-81C7-99E7050ACB1F}"/>
@@ -1447,6 +1459,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="About"/>
@@ -1762,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="79.7109375" bestFit="1" customWidth="1"/>
@@ -1892,6 +1905,14 @@
       <c r="B29" s="28">
         <f>1-B28</f>
         <v>0.18691815753258323</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -9585,7 +9606,7 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
@@ -9594,7 +9615,7 @@
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>249</v>
       </c>
@@ -9607,8 +9628,11 @@
       <c r="D1" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>250</v>
       </c>
@@ -9621,8 +9645,11 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>251</v>
       </c>
@@ -9635,8 +9662,11 @@
       <c r="D3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>252</v>
       </c>
@@ -9649,8 +9679,11 @@
       <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>253</v>
       </c>
@@ -9663,8 +9696,11 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>254</v>
       </c>
@@ -9677,8 +9713,11 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>255</v>
       </c>
@@ -9691,8 +9730,11 @@
       <c r="D7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>256</v>
       </c>
@@ -9708,8 +9750,11 @@
         <f>'Med- and Large-bldg Potential'!D53*10^3</f>
         <v>386500</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>257</v>
       </c>
@@ -9722,8 +9767,11 @@
       <c r="D9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>258</v>
       </c>
@@ -9736,8 +9784,11 @@
       <c r="D10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>259</v>
       </c>
@@ -9750,8 +9801,11 @@
       <c r="D11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>260</v>
       </c>
@@ -9764,8 +9818,11 @@
       <c r="D12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>261</v>
       </c>
@@ -9778,8 +9835,11 @@
       <c r="D13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>262</v>
       </c>
@@ -9792,8 +9852,11 @@
       <c r="D14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>263</v>
       </c>
@@ -9806,8 +9869,11 @@
       <c r="D15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>264</v>
       </c>
@@ -9820,8 +9886,11 @@
       <c r="D16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>265</v>
       </c>
@@ -9834,8 +9903,11 @@
       <c r="D17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>266</v>
       </c>
@@ -9848,8 +9920,11 @@
       <c r="D18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>267</v>
       </c>
@@ -9862,8 +9937,11 @@
       <c r="D19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>268</v>
       </c>
@@ -9876,8 +9954,11 @@
       <c r="D20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>269</v>
       </c>
@@ -9890,8 +9971,11 @@
       <c r="D21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>270</v>
       </c>
@@ -9904,8 +9988,11 @@
       <c r="D22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>271</v>
       </c>
@@ -9918,8 +10005,11 @@
       <c r="D23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>272</v>
       </c>
@@ -9932,8 +10022,11 @@
       <c r="D24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>273</v>
       </c>
@@ -9944,6 +10037,9 @@
         <v>0</v>
       </c>
       <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
         <v>0</v>
       </c>
     </row>
